--- a/data_u1/reporting_bias table_2025.01.16.xlsx
+++ b/data_u1/reporting_bias table_2025.01.16.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10329"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Desktop/LSR3_taar1_H_2025.04.01/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EAC55E-2923-9E4A-8E6E-A007CA25107E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B419B2-594E-0A45-AE6B-EE68B9785ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22740" yWindow="-17960" windowWidth="28800" windowHeight="16420" xr2:uid="{AFB5D0D2-F574-A541-B966-F5F755AA74BF}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{AFB5D0D2-F574-A541-B966-F5F755AA74BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="121">
   <si>
     <t>Study name</t>
   </si>
@@ -390,6 +390,15 @@
   </si>
   <si>
     <t>TAAR1 agonists vs. placebo (addon)</t>
+  </si>
+  <si>
+    <t>NCT06880328</t>
+  </si>
+  <si>
+    <t>? (study focusing on neuroimaging)</t>
+  </si>
+  <si>
+    <t>? (study focusing on neuroimaging, unclear if measured)</t>
   </si>
 </sst>
 </file>
@@ -517,59 +526,58 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1445,8 +1453,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D9E9CB4C-0556-F640-A49B-B9E2641DBBD7}" name="Table3" displayName="Table3" ref="A1:AI28" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
-  <autoFilter ref="A1:AI28" xr:uid="{D9E9CB4C-0556-F640-A49B-B9E2641DBBD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D9E9CB4C-0556-F640-A49B-B9E2641DBBD7}" name="Table3" displayName="Table3" ref="A1:AI29" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+  <autoFilter ref="A1:AI29" xr:uid="{D9E9CB4C-0556-F640-A49B-B9E2641DBBD7}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{97059465-C9E8-884E-B9D3-3FA8C407FE22}" name="Timepoint" dataDxfId="34"/>
     <tableColumn id="2" xr3:uid="{DCE35EE9-9321-5340-8F9E-118848FDEA36}" name="Study name" dataDxfId="33"/>
@@ -1805,47 +1813,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{137219A4-463B-B642-BF45-E469BD77CBE4}">
-  <dimension ref="A1:AI28"/>
+  <dimension ref="A1:AI29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="55.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5" style="7" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" style="7" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" style="7"/>
-    <col min="10" max="10" width="20.33203125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="21" style="7" customWidth="1"/>
-    <col min="12" max="12" width="23" style="7" customWidth="1"/>
-    <col min="13" max="13" width="22.5" style="7" customWidth="1"/>
-    <col min="14" max="14" width="28.1640625" style="7" customWidth="1"/>
-    <col min="15" max="15" width="31.6640625" style="7" customWidth="1"/>
-    <col min="16" max="16" width="20.1640625" style="7" customWidth="1"/>
-    <col min="17" max="17" width="22.83203125" style="7" customWidth="1"/>
-    <col min="18" max="18" width="26.6640625" style="7" customWidth="1"/>
-    <col min="19" max="20" width="20.6640625" style="7" customWidth="1"/>
-    <col min="21" max="21" width="31.1640625" style="7" customWidth="1"/>
-    <col min="22" max="22" width="23.6640625" style="7" customWidth="1"/>
-    <col min="23" max="23" width="25" style="7" customWidth="1"/>
-    <col min="24" max="24" width="27.5" style="7" customWidth="1"/>
-    <col min="25" max="26" width="11.6640625" style="7" customWidth="1"/>
-    <col min="27" max="27" width="10.83203125" style="7"/>
-    <col min="28" max="28" width="11.33203125" style="7" customWidth="1"/>
-    <col min="29" max="29" width="11.6640625" style="7" customWidth="1"/>
-    <col min="30" max="30" width="12.1640625" style="7" customWidth="1"/>
-    <col min="31" max="31" width="20.6640625" style="7" customWidth="1"/>
-    <col min="32" max="32" width="31.83203125" style="7" customWidth="1"/>
-    <col min="33" max="33" width="14.83203125" style="7" customWidth="1"/>
-    <col min="34" max="34" width="12" style="7" customWidth="1"/>
-    <col min="35" max="35" width="17" style="7" customWidth="1"/>
-    <col min="36" max="16384" width="10.83203125" style="7"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="2" max="2" width="55.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="20.33203125" customWidth="1"/>
+    <col min="11" max="11" width="21" customWidth="1"/>
+    <col min="12" max="12" width="23" customWidth="1"/>
+    <col min="13" max="13" width="22.5" customWidth="1"/>
+    <col min="14" max="14" width="28.1640625" customWidth="1"/>
+    <col min="15" max="15" width="31.6640625" customWidth="1"/>
+    <col min="16" max="16" width="20.1640625" customWidth="1"/>
+    <col min="17" max="17" width="22.83203125" customWidth="1"/>
+    <col min="18" max="18" width="26.6640625" customWidth="1"/>
+    <col min="19" max="20" width="20.6640625" customWidth="1"/>
+    <col min="21" max="21" width="31.1640625" customWidth="1"/>
+    <col min="22" max="22" width="23.6640625" customWidth="1"/>
+    <col min="23" max="23" width="25" customWidth="1"/>
+    <col min="24" max="24" width="27.5" customWidth="1"/>
+    <col min="25" max="26" width="11.6640625" customWidth="1"/>
+    <col min="28" max="28" width="11.33203125" customWidth="1"/>
+    <col min="29" max="29" width="11.6640625" customWidth="1"/>
+    <col min="30" max="30" width="12.1640625" customWidth="1"/>
+    <col min="31" max="31" width="20.6640625" customWidth="1"/>
+    <col min="32" max="32" width="31.83203125" customWidth="1"/>
+    <col min="33" max="33" width="14.83203125" customWidth="1"/>
+    <col min="34" max="34" width="12" customWidth="1"/>
+    <col min="35" max="35" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>70</v>
       </c>
       <c r="B1" s="6" t="s">
@@ -1860,99 +1865,99 @@
       <c r="E1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="Q1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="R1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="T1" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="U1" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="V1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="W1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="X1" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Y1" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="Z1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AA1" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AB1" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="AC1" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AD1" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="AE1" s="10" t="s">
+      <c r="AE1" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="AF1" s="10" t="s">
+      <c r="AF1" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="AG1" s="10" t="s">
+      <c r="AG1" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="AH1" s="10" t="s">
+      <c r="AH1" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="AI1" s="8" t="s">
+      <c r="AI1" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1967,7 +1972,7 @@
       <c r="E2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="12">
         <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -2059,7 +2064,7 @@
       </c>
     </row>
     <row r="3" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2074,7 +2079,7 @@
       <c r="E3" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="12">
         <v>48</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -2166,7 +2171,7 @@
       </c>
     </row>
     <row r="4" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2181,7 +2186,7 @@
       <c r="E4" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>48</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -2273,7 +2278,7 @@
       </c>
     </row>
     <row r="5" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2288,7 +2293,7 @@
       <c r="E5" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -2380,7 +2385,7 @@
       </c>
     </row>
     <row r="6" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -2395,7 +2400,7 @@
       <c r="E6" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -2487,14 +2492,14 @@
       </c>
     </row>
     <row r="7" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>118</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>114</v>
@@ -2502,103 +2507,103 @@
       <c r="E7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="13">
-        <v>16</v>
+      <c r="F7" s="12">
+        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>35</v>
+        <v>120</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AF7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI7" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>78</v>
@@ -2609,8 +2614,8 @@
       <c r="E8" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="13">
-        <v>49</v>
+      <c r="F8" s="12">
+        <v>16</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -2634,13 +2639,13 @@
         <v>34</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>35</v>
@@ -2701,11 +2706,11 @@
       </c>
     </row>
     <row r="9" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>78</v>
@@ -2716,8 +2721,8 @@
       <c r="E9" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="13">
-        <v>24</v>
+      <c r="F9" s="12">
+        <v>49</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -2740,23 +2745,23 @@
       <c r="M9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>30</v>
+      <c r="N9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>34</v>
@@ -2764,55 +2769,55 @@
       <c r="U9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="V9" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>30</v>
+      <c r="V9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB9" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="AB9" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="AD9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE9" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AF9" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="AE9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF9" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>78</v>
@@ -2823,8 +2828,8 @@
       <c r="E10" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F10" s="13">
-        <v>64</v>
+      <c r="F10" s="12">
+        <v>24</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -2847,23 +2852,23 @@
       <c r="M10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="N10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>32</v>
+      <c r="N10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="T10" s="2" t="s">
         <v>34</v>
@@ -2871,55 +2876,55 @@
       <c r="U10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="V10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>32</v>
+      <c r="V10" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB10" s="2" t="s">
-        <v>32</v>
+        <v>56</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="AD10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF10" s="2" t="s">
-        <v>32</v>
+        <v>56</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>78</v>
@@ -2930,8 +2935,8 @@
       <c r="E11" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F11" s="13">
-        <v>164</v>
+      <c r="F11" s="12">
+        <v>64</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -2955,78 +2960,78 @@
         <v>34</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="AD11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="AE11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="AG11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>78</v>
@@ -3037,8 +3042,8 @@
       <c r="E12" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F12" s="13">
-        <v>52</v>
+      <c r="F12" s="12">
+        <v>164</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>34</v>
@@ -3062,78 +3067,78 @@
         <v>34</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="AG12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>78</v>
@@ -3144,8 +3149,8 @@
       <c r="E13" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F13" s="13">
-        <v>69</v>
+      <c r="F13" s="12">
+        <v>52</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -3168,23 +3173,23 @@
       <c r="M13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="N13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>30</v>
+      <c r="N13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>34</v>
@@ -3193,57 +3198,57 @@
         <v>34</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB13" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="AB13" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD13" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="AD13" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AI13" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="AH13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI13" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>72</v>
+      <c r="A14" s="10" t="s">
+        <v>71</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>114</v>
@@ -3251,29 +3256,29 @@
       <c r="E14" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="13">
-        <v>39</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>30</v>
+      <c r="F14" s="12">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>30</v>
@@ -3294,50 +3299,52 @@
         <v>30</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="W14" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="X14" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="AA14" s="2" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG14" s="3" t="s">
-        <v>30</v>
+      <c r="AC14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AI14" s="2" t="s">
-        <v>32</v>
+      <c r="AI14" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -3345,212 +3352,210 @@
         <v>72</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="13">
-        <v>28</v>
+      <c r="F15" s="12">
+        <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="W15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA15" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="AB15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AC15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD15" s="2" t="s">
         <v>32</v>
       </c>
       <c r="AE15" s="3" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="AG15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI15" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:35" s="4" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>72</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="13">
-        <v>245</v>
+      <c r="F16" s="12">
+        <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>68</v>
+        <v>32</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="W16" s="2" t="s">
-        <v>92</v>
+        <v>32</v>
+      </c>
+      <c r="W16" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AB16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AC16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AD16" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE16" s="3" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="AF16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI16" s="3" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3559,7 +3564,7 @@
         <v>72</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>76</v>
@@ -3570,8 +3575,8 @@
       <c r="E17" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F17" s="13">
-        <v>463</v>
+      <c r="F17" s="12">
+        <v>245</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>30</v>
@@ -3582,89 +3587,91 @@
       <c r="I17" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>31</v>
+      <c r="J17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="O17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>87</v>
+      <c r="O17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="X17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA17" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB17" s="2"/>
-      <c r="AC17" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD17" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AF17" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF17" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="AG17" s="2" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="AI17" s="2" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" s="4" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>72</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>76</v>
@@ -3675,8 +3682,8 @@
       <c r="E18" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F18" s="13">
-        <v>435</v>
+      <c r="F18" s="12">
+        <v>463</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>30</v>
@@ -3720,7 +3727,9 @@
       <c r="T18" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="U18" s="2"/>
+      <c r="U18" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="V18" s="2" t="s">
         <v>87</v>
       </c>
@@ -3728,7 +3737,7 @@
         <v>87</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="Y18" s="2" t="s">
         <v>61</v>
@@ -3767,7 +3776,7 @@
         <v>72</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>76</v>
@@ -3778,95 +3787,91 @@
       <c r="E19" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F19" s="13">
-        <v>83</v>
+      <c r="F19" s="12">
+        <v>435</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>112</v>
+      <c r="J19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>62</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>32</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="U19" s="2"/>
       <c r="V19" s="2" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="AA19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD19" s="3" t="s">
-        <v>32</v>
+        <v>60</v>
+      </c>
+      <c r="AB19" s="2"/>
+      <c r="AC19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD19" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="AE19" s="2" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI19" s="3" t="s">
-        <v>32</v>
+        <v>87</v>
+      </c>
+      <c r="AH19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI19" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -3874,7 +3879,7 @@
         <v>72</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>76</v>
@@ -3885,53 +3890,53 @@
       <c r="E20" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F20" s="13">
-        <v>213</v>
+      <c r="F20" s="12">
+        <v>83</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>98</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="V20" s="2" t="s">
         <v>32</v>
@@ -3945,20 +3950,20 @@
       <c r="Y20" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB20" s="2" t="s">
+      <c r="Z20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="AC20" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AD20" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE20" s="2" t="s">
         <v>32</v>
@@ -3969,22 +3974,22 @@
       <c r="AG20" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI20" s="2" t="s">
+      <c r="AH20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI20" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="5" t="s">
         <v>72</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>109</v>
+        <v>6</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>114</v>
@@ -3992,53 +3997,53 @@
       <c r="E21" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F21" s="13">
-        <v>60</v>
+      <c r="F21" s="12">
+        <v>213</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>32</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U21" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="V21" s="2" t="s">
         <v>32</v>
@@ -4052,20 +4057,20 @@
       <c r="Y21" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="Z21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB21" s="3" t="s">
+      <c r="Z21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB21" s="2" t="s">
         <v>32</v>
       </c>
       <c r="AC21" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AD21" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE21" s="2" t="s">
         <v>32</v>
@@ -4076,22 +4081,22 @@
       <c r="AG21" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI21" s="3" t="s">
+      <c r="AH21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI21" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="10" t="s">
         <v>72</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>114</v>
@@ -4099,427 +4104,427 @@
       <c r="E22" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="12">
+        <v>60</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI22" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="12">
         <v>27</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H22" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J22" s="3" t="s">
+      <c r="I23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="L22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M22" s="2" t="s">
+      <c r="L23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="N23" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="O22" s="3" t="s">
+      <c r="O23" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="P22" s="3" t="s">
+      <c r="P23" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="Q22" s="3" t="s">
+      <c r="Q23" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="R22" s="3" t="s">
+      <c r="R23" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="S23" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="T22" s="2" t="s">
+      <c r="T23" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="U22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X22" s="2" t="s">
+      <c r="U23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="X23" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="Y22" s="2" t="s">
+      <c r="Y23" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="Z22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AI22" s="3" t="s">
+      <c r="Z23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI23" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:35" s="25" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
+    <row r="24" spans="1:35" s="24" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B24" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C24" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D24" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E24" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="F23" s="22">
+      <c r="F24" s="21">
         <v>104</v>
       </c>
-      <c r="G23" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="H23" s="23" t="s">
+      <c r="G24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="I23" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="J23" s="23" t="s">
+      <c r="I24" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="K23" s="23" t="s">
+      <c r="K24" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="L23" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="M23" s="24" t="s">
+      <c r="L24" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="M24" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="N23" s="23" t="s">
+      <c r="N24" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="O23" s="23" t="s">
+      <c r="O24" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="P23" s="23" t="s">
+      <c r="P24" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="Q23" s="23" t="s">
+      <c r="Q24" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="R23" s="23" t="s">
+      <c r="R24" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="S23" s="23" t="s">
+      <c r="S24" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="T23" s="24" t="s">
+      <c r="T24" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="U23" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="V23" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="W23" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="X23" s="24" t="s">
+      <c r="U24" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="V24" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="W24" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="X24" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Y23" s="24" t="s">
+      <c r="Y24" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="Z23" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA23" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB23" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC23" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD23" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE23" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF23" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG23" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH23" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="AI23" s="23" t="s">
+      <c r="Z24" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA24" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE24" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF24" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG24" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI24" s="22" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:35" s="19" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A24" s="14" t="s">
+    <row r="25" spans="1:35" s="18" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B25" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C25" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D25" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E25" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F25" s="15">
         <v>31</v>
       </c>
-      <c r="G24" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="H24" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="I24" s="17" t="s">
+      <c r="G25" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="J24" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="K24" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L24" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="M24" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="N24" s="18" t="s">
+      <c r="J25" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="N25" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="O24" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="P24" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q24" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="R24" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="S24" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="T24" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="U24" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="V24" s="17" t="s">
+      <c r="O25" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="P25" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q25" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="R25" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="S25" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="T25" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="U25" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="V25" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="W24" s="17" t="s">
+      <c r="W25" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="X24" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y24" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z24" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA24" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB24" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC24" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD24" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE24" s="17" t="s">
+      <c r="X25" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y25" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z25" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA25" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB25" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC25" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD25" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE25" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="AF24" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG24" s="17" t="s">
+      <c r="AF25" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG25" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="AH24" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="AI24" s="17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F25" s="13">
-        <v>70</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="U25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="W25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="X25" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y25" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z25" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA25" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC25" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG25" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AI25" s="3" t="s">
-        <v>30</v>
+      <c r="AH25" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI25" s="16" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
-        <v>72</v>
+      <c r="A26" s="10" t="s">
+        <v>71</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>114</v>
@@ -4527,29 +4532,29 @@
       <c r="E26" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F26" s="13">
-        <v>214</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>30</v>
+      <c r="F26" s="12">
+        <v>70</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>30</v>
@@ -4569,53 +4574,53 @@
       <c r="S26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>30</v>
+      <c r="T26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="V26" s="2" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC26" s="3" t="s">
-        <v>30</v>
+        <v>85</v>
+      </c>
+      <c r="Z26" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA26" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC26" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="AD26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AE26" s="2" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="AF26" s="2" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="AG26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI26" s="2" t="s">
-        <v>32</v>
+        <v>85</v>
+      </c>
+      <c r="AH26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI26" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -4623,10 +4628,10 @@
         <v>72</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>114</v>
@@ -4634,53 +4639,53 @@
       <c r="E27" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F27" s="13">
-        <v>19</v>
+      <c r="F27" s="12">
+        <v>214</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>32</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="T27" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U27" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="V27" s="2" t="s">
         <v>32</v>
@@ -4694,20 +4699,20 @@
       <c r="Y27" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="Z27" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA27" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB27" s="3" t="s">
+      <c r="Z27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB27" s="2" t="s">
         <v>32</v>
       </c>
       <c r="AC27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AD27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE27" s="2" t="s">
         <v>32</v>
@@ -4718,19 +4723,19 @@
       <c r="AG27" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI27" s="3" t="s">
+      <c r="AH27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI27" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:35" s="4" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:35" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>77</v>
@@ -4741,94 +4746,201 @@
       <c r="E28" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="12">
+        <v>19</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="W28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="X28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI28" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:35" s="4" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="12">
         <v>303</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
+      <c r="H29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="K29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="L28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="U28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="V28" s="2" t="s">
+      <c r="L29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="V29" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="W28" s="2" t="s">
+      <c r="W29" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="X28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG28" s="2" t="s">
+      <c r="X29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG29" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AH28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI28" s="3" t="s">
+      <c r="AH29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI29" s="3" t="s">
         <v>30</v>
       </c>
     </row>
